--- a/apps/web/public/templates/06_أمر_التكليف.xlsx
+++ b/apps/web/public/templates/06_أمر_التكليف.xlsx
@@ -253,31 +253,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>لازم يكون موجود في مقايسة العقد</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>بيتجاب من العقد — مش بيتقرا</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>اختياري: #75 — لو الكميات متقسمة على مواقع</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +962,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1070,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1177,6 +1151,37 @@
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• [بنود أمر التكليف] رقم البند: لازم يكون موجود في مقايسة العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>• [بنود أمر التكليف] الوصف (للمراجعة فقط): بيتجاب من العقد — مش بيتقرا</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• [بنود أمر التكليف] كود الموقع / الكابينة: اختياري: #75 — لو الكميات متقسمة على مواقع</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,6 +1223,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"بنود أمر التكليف": [["1-7-2", "الحفر للشبكة الثانوية", "#75", "133.77"], ["1-9-1", "حفر ضيق Micro trenching", "#75", "1292"]], "مهمات أمر التكليف": [["1.1.7", "48 FIBER OPTIC CABLE", "12.5"]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/06_أمر_التكليف.xlsx
+++ b/apps/web/public/templates/06_أمر_التكليف.xlsx
@@ -618,7 +618,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>رقم الملحق / الزيادة</t>
+          <t>رقم ملحق أمر التكليف</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>0 = الأصلي، 1 = أول ملحق زيادة ...</t>
+          <t>0 = أمر التكليف الأصلي، 1 = ملحق الزيادة الأول ...</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>من قالب المشروعات</t>
+          <t>من نموذج المشروعات</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>لو فاضي بتتحسب من الكميات × أسعار العقد</t>
+          <t>إذا تُركت فارغة تُحتسب من الكميات × أسعار العقد</t>
         </is>
       </c>
     </row>
@@ -721,14 +721,14 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>للملاحق بس</t>
+          <t>للملاحق فقط</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>الالتزام المالي المعتمد</t>
+          <t>الارتباط المالي المعتمد</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ممكن يبقى أقل من قيمة أمر التكليف — المستخلصات مش بتعدّيه من غير تجديد</t>
+          <t>قد يقل عن قيمة أمر التكليف — ولا يجوز أن تتجاوزه المستخلصات دون تعزيز الارتباط المالي</t>
         </is>
       </c>
     </row>
@@ -757,14 +757,14 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>بيتصرف 100% بعد الانتهاء</t>
+          <t>يُسدَّد بنسبة 100% بعد الانتهاء</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>النطاق / المنطقة</t>
+          <t>النطاق الجغرافي / المنطقة</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>نعم / لا — لو نعم بتتطبق علاوة خارج النطاق</t>
+          <t>نعم / لا — في حال «نعم» تُطبَّق علاوة خارج النطاق</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>إجمالي الدمغات المسددة</t>
+          <t>إجمالي رسوم الدمغة المسددة</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr"/>
@@ -957,7 +957,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1030,7 +1030,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C3:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="C3:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1053,21 +1053,21 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>قالب أمر التكليف</t>
+          <t>نموذج أمر التكليف</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>الغرض: تعريف أمر التكليف وكمياته المخططة لكل بند (ولكل موقع لو موجود) والمهمات المخططة.</t>
+          <t>الغرض: تعريف أمر التكليف وكمياته المخططة لكل بند (ولكل موقع إن وُجد) والمهمات المخططة.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>مين بيرفعه: الشئون الفنية.</t>
+          <t>الجهة المسؤولة عن الرفع: الشئون الفنية.</t>
         </is>
       </c>
     </row>
@@ -1077,28 +1077,28 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>• أمر التكليف بيتربط بمشروع، ومنه بيتعرف السنترال والإدارة والقطاع.</t>
+          <t>• يرتبط أمر التكليف بمشروع، يتحدد من خلاله السنترال والإدارة والقطاع.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>• ملحق الزيادة بيترفع بنفس القالب مع رقم الملحق — السيستم بيحتفظ بالأصل والزيادة.</t>
+          <t>• يُرفع ملحق أمر التكليف بالنموذج نفسه مع رقم الملحق — وتحتفظ المنظومة بالقيمة الأصلية والزيادة.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>• ممكن الكميات تبقى أعمدة لكل موقع (#75، #76...) زي ملفات الزيادة — في الحالة دي حط كل موقع في صف مع كود الموقع.</t>
+          <t>• إذا كانت الكميات موزعة في أعمدة لكل موقع (#75، #76...) كما في ملفات الزيادة، يرجى إدراج كل موقع في صف مستقل مع كود الموقع.</t>
         </is>
       </c>
     </row>
@@ -1108,49 +1108,49 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -1160,28 +1160,28 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>• [بنود أمر التكليف] رقم البند: لازم يكون موجود في مقايسة العقد</t>
+          <t>• [بنود أمر التكليف] رقم البند: يجب أن يكون مدرجاً في جدول كميات العقد</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• [بنود أمر التكليف] الوصف (للمراجعة فقط): بيتجاب من العقد — مش بيتقرا</t>
+          <t>• [بنود أمر التكليف] الوصف (للمراجعة فقط): يُستمد من العقد — ولا يُقرأ من هذا العمود</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• [بنود أمر التكليف] كود الموقع / الكابينة: اختياري: #75 — لو الكميات متقسمة على مواقع</t>
+          <t>• [بنود أمر التكليف] كود الموقع / الكابينة: اختياري: #75 — في حال توزيع الكميات على مواقع</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/templates/06_أمر_التكليف.xlsx
+++ b/apps/web/public/templates/06_أمر_التكليف.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>الحفر للشبكة الثانوية</t>
+          <t>مثال — الحفر للشبكة الثانوية</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>حفر ضيق Micro trenching</t>
+          <t>مثال — حفر ضيق Micro trenching</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>48 FIBER OPTIC CABLE</t>
+          <t>مثال — 48 FIBER OPTIC CABLE</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"بنود أمر التكليف": [["1-7-2", "الحفر للشبكة الثانوية", "#75", "133.77"], ["1-9-1", "حفر ضيق Micro trenching", "#75", "1292"]], "مهمات أمر التكليف": [["1.1.7", "48 FIBER OPTIC CABLE", "12.5"]]}</t>
+          <t>{"بنود أمر التكليف": [["1-7-2", "مثال — الحفر للشبكة الثانوية", "#75", "133.77"], ["1-9-1", "مثال — حفر ضيق Micro trenching", "#75", "1292"]], "مهمات أمر التكليف": [["1.1.7", "مثال — 48 FIBER OPTIC CABLE", "12.5"]]}</t>
         </is>
       </c>
     </row>
